--- a/survey_templates/044_student_skills_and_goals_survey--survey_templates.xlsx
+++ b/survey_templates/044_student_skills_and_goals_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -665,8 +665,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -694,12 +694,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'communication'}</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Communication'}</t>
+          <t>Communication</t>
         </is>
       </c>
     </row>
@@ -711,12 +711,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'teamwork'}</t>
+          <t>teamwork</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Teamwork'}</t>
+          <t>Teamwork</t>
         </is>
       </c>
     </row>
@@ -728,12 +728,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'problem_solving'}</t>
+          <t>problem_solving</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Problem Solving'}</t>
+          <t>Problem Solving</t>
         </is>
       </c>
     </row>
@@ -745,12 +745,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'time_management'}</t>
+          <t>time_management</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Time Management'}</t>
+          <t>Time Management</t>
         </is>
       </c>
     </row>
@@ -762,12 +762,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'adaptability'}</t>
+          <t>adaptability</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Adaptability'}</t>
+          <t>Adaptability</t>
         </is>
       </c>
     </row>
@@ -779,12 +779,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'leadership'}</t>
+          <t>leadership</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Leadership'}</t>
+          <t>Leadership</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'creativity'}</t>
+          <t>creativity</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Creativity'}</t>
+          <t>Creativity</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'critical_thinking'}</t>
+          <t>critical_thinking</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Critical Thinking'}</t>
+          <t>Critical Thinking</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'innovation'}</t>
+          <t>innovation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Innovation'}</t>
+          <t>Innovation</t>
         </is>
       </c>
     </row>
@@ -847,12 +847,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'online_learning'}</t>
+          <t>online_learning</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Online Learning'}</t>
+          <t>Online Learning</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'in_person'}</t>
+          <t>in_person</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'In Person'}</t>
+          <t>In Person</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'hybrid'}</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Hybrid'}</t>
+          <t>Hybrid</t>
         </is>
       </c>
     </row>
@@ -898,12 +898,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'self-paced'}</t>
+          <t>self-paced</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Self-Paced'}</t>
+          <t>Self-Paced</t>
         </is>
       </c>
     </row>
@@ -915,12 +915,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'project-based'}</t>
+          <t>project-based</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Project-Based'}</t>
+          <t>Project-Based</t>
         </is>
       </c>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'academic_achievement'}</t>
+          <t>academic_achievement</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Academic Achievement'}</t>
+          <t>Academic Achievement</t>
         </is>
       </c>
     </row>
@@ -949,12 +949,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'career_development'}</t>
+          <t>career_development</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Career Development'}</t>
+          <t>Career Development</t>
         </is>
       </c>
     </row>
@@ -966,12 +966,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'character_education'}</t>
+          <t>character_education</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Character Education'}</t>
+          <t>Character Education</t>
         </is>
       </c>
     </row>
@@ -983,12 +983,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'social_responsibility'}</t>
+          <t>social_responsibility</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Social Responsibility'}</t>
+          <t>Social Responsibility</t>
         </is>
       </c>
     </row>
